--- a/data/pedidos_ecomarket.xlsx
+++ b/data/pedidos_ecomarket.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icesiedu-my.sharepoint.com/personal/1030617659_u_icesi_edu_co/Documents/Semestre 3/IA Generativa/ecomarket-rag-solution/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DE4889-02FD-4F2C-ADE8-BC781539DBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -507,7 +507,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -541,7 +541,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
